--- a/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/JLCPCB-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
+++ b/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/JLCPCB-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\LocAl\SamirAbiNahed-DigitalTasbeeh\PCB\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C875F5B5-1D7C-4B51-A1EC-43D2F007B6C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B563FAEB-9287-4676-9056-20F434CF10BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
   <si>
     <t>Comment</t>
   </si>
@@ -205,9 +205,6 @@
     <t>C106225</t>
   </si>
   <si>
-    <t>C226462</t>
-  </si>
-  <si>
     <t>C106227</t>
   </si>
   <si>
@@ -233,6 +230,12 @@
   </si>
   <si>
     <t>C295786</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>C166301</t>
   </si>
 </sst>
 </file>
@@ -282,7 +285,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -364,11 +367,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -390,6 +404,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,7 +695,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -687,7 +704,7 @@
     <col min="4" max="4" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -700,8 +717,11 @@
       <c r="D1" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -712,10 +732,13 @@
         <v>41</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -728,8 +751,11 @@
       <c r="D3" s="6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -740,10 +766,13 @@
         <v>43</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
@@ -756,8 +785,11 @@
       <c r="D5" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -770,8 +802,11 @@
       <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -782,10 +817,13 @@
         <v>6</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -798,8 +836,11 @@
       <c r="D8" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -812,8 +853,11 @@
       <c r="D9" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -824,10 +868,13 @@
         <v>47</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
@@ -840,8 +887,11 @@
       <c r="D11" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -854,8 +904,11 @@
       <c r="D12" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
@@ -868,8 +921,11 @@
       <c r="D13" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -882,8 +938,11 @@
       <c r="D14" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
@@ -894,10 +953,13 @@
         <v>47</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -908,10 +970,13 @@
         <v>47</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
@@ -922,10 +987,13 @@
         <v>47</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -936,10 +1004,13 @@
         <v>48</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
@@ -950,10 +1021,13 @@
         <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
@@ -964,7 +1038,10 @@
         <v>50</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/JLCPCB-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
+++ b/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/JLCPCB-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\LocAl\SamirAbiNahed-DigitalTasbeeh\PCB\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\Git_Repo\SamirAbiNahed-DigitalTasbeeh\Design Files\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B563FAEB-9287-4676-9056-20F434CF10BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D547FE-2BBF-418A-BBFE-3D26F75C8426}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="76">
   <si>
     <t>Comment</t>
   </si>
@@ -236,6 +236,18 @@
   </si>
   <si>
     <t>C166301</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>TP1</t>
+  </si>
+  <si>
+    <t>LCM0720A3134F</t>
+  </si>
+  <si>
+    <t>C2895081</t>
   </si>
 </sst>
 </file>
@@ -382,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -407,6 +419,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,7 +710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1044,6 +1059,23 @@
         <v>1</v>
       </c>
     </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/JLCPCB-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
+++ b/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/JLCPCB-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\Git_Repo\SamirAbiNahed-DigitalTasbeeh\Design Files\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\LocAl\SamirAbiNahed-DigitalTasbeeh\PCB\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D547FE-2BBF-418A-BBFE-3D26F75C8426}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413507DB-5BE9-4B50-9FD7-0918015A6B76}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="75">
   <si>
     <t>Comment</t>
   </si>
@@ -73,9 +73,6 @@
     <t>13.3k</t>
   </si>
   <si>
-    <t>EVQ-PLHA15</t>
-  </si>
-  <si>
     <t>ATTINY1616-MNR</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>R16</t>
   </si>
   <si>
-    <t>SW1</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -166,9 +160,6 @@
     <t>Res-0201</t>
   </si>
   <si>
-    <t>EVQPLH_PAN</t>
-  </si>
-  <si>
     <t>VQFN-20-EP(3x3)</t>
   </si>
   <si>
@@ -211,9 +202,6 @@
     <t>C423749</t>
   </si>
   <si>
-    <t>C79172</t>
-  </si>
-  <si>
     <t>C507118</t>
   </si>
   <si>
@@ -248,6 +236,15 @@
   </si>
   <si>
     <t>C2895081</t>
+  </si>
+  <si>
+    <t>GT-TC084A-H015-L5</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>C778172</t>
   </si>
 </sst>
 </file>
@@ -724,16 +721,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -741,13 +738,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -758,13 +755,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -775,13 +772,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -792,13 +789,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -809,13 +806,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -826,13 +823,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -843,13 +840,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -860,13 +857,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -877,13 +874,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -894,13 +891,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -911,13 +908,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -928,13 +925,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -945,13 +942,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -962,13 +959,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -979,13 +976,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -996,13 +993,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1010,16 +1007,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1027,16 +1024,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1044,16 +1041,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1061,16 +1058,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E21">
         <v>1</v>
